--- a/ttl_long/AdHoc_Net_9.xlsx
+++ b/ttl_long/AdHoc_Net_9.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>159</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>283</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>271</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>330</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>355</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>496</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>514</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>578</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>604</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>683</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>737</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>732</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>929</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>836</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>283</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>868</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1081</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1125</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1150</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1285</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1188</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1439</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>167</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1287</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1306</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1550</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1430</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1526</t>
         </is>
       </c>
     </row>
@@ -1004,114 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1430</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1553</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1628</t>
+          <t>682</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,7 +1057,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1181,7 +1079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1203,7 +1101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1225,7 +1123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1247,7 +1145,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1269,7 +1167,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1291,7 +1189,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1313,7 +1211,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1335,7 +1233,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1357,7 +1255,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1374,7 +1272,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1401,7 +1299,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1423,7 +1321,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1440,12 +1338,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1462,12 +1360,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1484,7 +1382,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1506,12 +1404,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,12 +1426,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,12 +1448,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,12 +1492,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1616,12 +1514,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1638,12 +1536,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1665,7 +1563,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1682,12 +1580,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1704,12 +1602,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1726,12 +1624,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1748,12 +1646,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1770,12 +1668,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1792,12 +1690,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1814,12 +1712,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1836,12 +1734,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1858,12 +1756,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1880,12 +1778,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1902,12 +1800,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1924,12 +1822,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1946,12 +1844,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1968,12 +1866,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1990,12 +1888,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2012,12 +1910,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2034,12 +1932,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2056,12 +1954,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2078,12 +1976,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2100,7 +1998,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2122,12 +2020,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2144,12 +2042,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2166,12 +2064,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2188,7 +2086,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2210,12 +2108,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2232,12 +2130,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2254,12 +2152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2276,12 +2174,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2298,12 +2196,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2320,12 +2218,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2342,12 +2240,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2364,12 +2262,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2386,12 +2284,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2408,12 +2306,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2430,12 +2328,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2452,12 +2350,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2474,12 +2372,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2496,12 +2394,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2518,12 +2416,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2540,12 +2438,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2562,12 +2460,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2584,12 +2482,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2606,12 +2504,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2628,12 +2526,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2650,12 +2548,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2672,12 +2570,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2694,12 +2592,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2716,12 +2614,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2738,12 +2636,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2760,12 +2658,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2782,12 +2680,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2804,12 +2702,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2826,12 +2724,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2848,12 +2746,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,12 +2768,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2892,12 +2790,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2914,12 +2812,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2936,12 +2834,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2958,12 +2856,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2972,622 +2870,6 @@
         </is>
       </c>
       <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3626,7 +2908,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3636,7 +2918,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -3662,7 +2944,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_9.xlsx
+++ b/ttl_long/AdHoc_Net_9.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>554</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>331</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>286</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>391</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>558</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>243</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>441</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>472</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>635</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>587</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>626</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>785</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>780</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>762</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>933</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>266</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>863</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>339</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>836</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1048</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1031</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1006</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1205</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1149</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1143</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1191</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1247</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1257</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,131 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1376</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1553</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1542</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1670</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1101,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1123,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1206,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1233,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1255,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1272,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1299,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1321,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1338,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1360,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1382,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1404,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1431,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1448,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1470,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1492,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1514,7 +1633,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1536,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1558,7 +1677,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1602,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1624,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1646,7 +1765,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1668,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1690,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1712,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1734,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1756,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1778,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1800,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1822,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1844,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1866,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1888,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1910,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1932,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1954,7 +2073,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1976,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1998,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2020,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2042,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2064,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2086,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2108,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2130,7 +2249,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2152,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2174,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2196,7 +2315,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2218,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2240,7 +2359,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2262,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2284,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2306,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2328,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2350,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2372,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2416,7 +2535,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2438,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2460,7 +2579,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2482,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2504,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2526,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2548,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2570,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2592,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2636,7 +2755,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2658,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2702,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2724,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2746,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2790,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2812,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2834,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2856,20 +2975,680 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2918,7 +3697,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2938,7 +3717,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_9.xlsx
+++ b/ttl_long/AdHoc_Net_9.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>218</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>289</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>353</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>405</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>444</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>429</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>530</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>625</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>551</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>318</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>602</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>697</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>315</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>723</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>943</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>889</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>989</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1019</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1175</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1163</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1102</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1176</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>193</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1313</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>319</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1210</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1293</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1364</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1344</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1490</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1507</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1635</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1589</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,7 +2249,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,7 +2909,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,20 +3635,130 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3687,7 +3797,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
